--- a/input/old/Metadata _SOD_ GR_IR vs PO user comparison_200025_001415.xlsx
+++ b/input/old/Metadata _SOD_ GR_IR vs PO user comparison_200025_001415.xlsx
@@ -430,7 +430,7 @@
         <v>Updated on</v>
       </c>
       <c r="B7" t="str">
-        <v>18.12.2025 at 11:32 by ILIYAR</v>
+        <v>18.12.2025 at 11:32 by REDACTED</v>
       </c>
     </row>
     <row r="8">
